--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\nbcamp\AirNHook\Assets\StreamingAssets\Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A68270-E2E3-42FD-AC24-7CCA3F6FEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA2602E-E98B-466B-BB7B-58919C78160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22410" yWindow="3690" windowWidth="21600" windowHeight="11340" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="4680" yWindow="1545" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Esc를 눌러 종료</t>
   </si>
@@ -151,15 +151,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이 옵션은 메뉴에서 사용할 수 없습니다</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>전체화면</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>마스터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맵 에디터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 옵션은 현재 사용할 수 없습니다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 시작</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -601,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -668,7 +676,7 @@
         <v>1006</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" thickBot="1">
@@ -676,7 +684,7 @@
         <v>1007</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" thickBot="1">
@@ -732,7 +740,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" thickBot="1">
@@ -809,17 +817,33 @@
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>2010</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
+        <v>2101</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A28" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A29" s="1">
         <v>4002</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA2602E-E98B-466B-BB7B-58919C78160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7A8A87-F8A2-4B2D-84A3-F3B256DFC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1545" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="2550" yWindow="1140" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Esc를 눌러 종료</t>
   </si>
@@ -168,6 +168,10 @@
   </si>
   <si>
     <t>스테이지 시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -609,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -743,107 +747,115 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" thickBot="1">
+    <row r="17" spans="1:2" ht="28.5" thickBot="1">
       <c r="A17" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
+        <v>1015</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" thickBot="1">
       <c r="A18" s="1">
-        <v>2002</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
+        <v>2001</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>8</v>
+        <v>2002</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2005</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>2004</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>2006</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>2009</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>13</v>
+        <v>2101</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A30" s="1">
         <v>4002</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7A8A87-F8A2-4B2D-84A3-F3B256DFC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7E1E60-5103-4185-A0CC-F4BD6F7CA0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1140" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="2895" yWindow="1485" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Esc를 눌러 종료</t>
   </si>
@@ -172,6 +172,10 @@
   </si>
   <si>
     <t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인게임에서는 비활성화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -613,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -757,105 +761,113 @@
     </row>
     <row r="18" spans="1:2" ht="17.25" thickBot="1">
       <c r="A18" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
+        <v>1016</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2002</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>2001</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>2002</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2005</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>2004</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>10</v>
+        <v>2006</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>2009</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>13</v>
+        <v>2101</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" thickBot="1">
       <c r="A30" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A31" s="1">
         <v>4002</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7E1E60-5103-4185-A0CC-F4BD6F7CA0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D87EB8-7C8C-43D8-849B-AC63D292249A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2895" yWindow="1485" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Esc를 눌러 종료</t>
   </si>
@@ -176,6 +176,10 @@
   </si>
   <si>
     <t>인게임에서는 비활성화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>접속 코드</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -617,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -769,105 +773,113 @@
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
+        <v>1017</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2002</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>24</v>
+        <v>2001</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
+        <v>2002</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2005</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>2004</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>2006</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>2010</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>27</v>
+        <v>2009</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" thickBot="1">
       <c r="A30" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>13</v>
+        <v>2101</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" thickBot="1">
       <c r="A31" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A32" s="1">
         <v>4002</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -13,39 +13,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <x:si>
+    <x:t>네 멍청한 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
   <x:si>
     <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
   </x:si>
   <x:si>
+    <x:t>좋아, 콩알 파이프를 활성화하게 되면, 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
   </x:si>
   <x:si>
+    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vsync</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
     <x:t>코드 입력</x:t>
   </x:si>
   <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
     <x:t>전체화면</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -74,70 +143,31 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
     <x:t>맵 에디터</x:t>
   </x:si>
   <x:si>
-    <x:t>로딩중...</x:t>
+    <x:t>슈퍼 솔저 캠프에 온 것을 환영한다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
   </x:si>
   <x:si>
     <x:t>스테이지 재시작</x:t>
   </x:si>
   <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
+  </x:si>
+  <x:si>
     <x:t>Esc를 눌러 종료</x:t>
   </x:si>
   <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
     <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국어</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -316,7 +346,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -361,7 +390,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -438,7 +466,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -477,7 +504,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -500,7 +526,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -533,7 +558,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -581,7 +605,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -637,7 +660,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -672,7 +694,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -705,7 +726,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -728,7 +748,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -762,7 +781,7 @@
       </x:fill>
     </x:dxf>
   </x:dxfs>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="PivotStyleLight16" pivot="1" table="0" count="11">
       <x:tableStyleElement type="headerRow" size="1" dxfId="0"/>
       <x:tableStyleElement type="totalRow" size="1" dxfId="1"/>
@@ -1101,19 +1120,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B33"/>
+  <x:dimension ref="A1:B43"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="51.5" customWidth="1"/>
+    <x:col min="2" max="2" width="86.18359375" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1121,7 +1140,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1129,7 +1148,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1137,7 +1156,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1145,7 +1164,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1153,7 +1172,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1161,7 +1180,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1169,7 +1188,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1177,7 +1196,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1185,7 +1204,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1193,7 +1212,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1201,7 +1220,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1209,7 +1228,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1217,7 +1236,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1225,7 +1244,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1233,15 +1252,15 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:2" ht="27.399999999999999">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
       <x:c r="A17" s="1">
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1249,7 +1268,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1257,7 +1276,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1265,7 +1284,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2" ht="17.149999999999999">
@@ -1273,7 +1292,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1281,7 +1300,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1289,7 +1308,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1297,7 +1316,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1305,7 +1324,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1313,7 +1332,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1321,7 +1340,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1329,7 +1348,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1337,7 +1356,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1345,7 +1364,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1353,7 +1372,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1361,7 +1380,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1369,11 +1388,91 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:2">
+      <x:c r="A34">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:2">
+      <x:c r="A35">
+        <x:v>10002</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:2">
+      <x:c r="A36">
+        <x:v>10003</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:2">
+      <x:c r="A37">
+        <x:v>10004</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" spans="1:2">
+      <x:c r="A38">
+        <x:v>10005</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:2">
+      <x:c r="A39">
+        <x:v>10006</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:2">
+      <x:c r="A40">
+        <x:v>10007</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:2">
+      <x:c r="A41">
+        <x:v>10008</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:2">
+      <x:c r="A42">
+        <x:v>10009</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:2">
+      <x:c r="A43">
+        <x:v>10010</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fileVersion appName="HCell" lastEdited="9.0" lowestEdited="9.0" rupBuild="0.568"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28365" windowHeight="8280"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="14985" windowHeight="9030"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <x:si>
     <x:t>네 멍청한 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
   </x:si>
   <x:si>
-    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
   </x:si>
   <x:si>
     <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
@@ -27,94 +27,94 @@
     <x:t>좋아, 콩알 파이프를 활성화하게 되면, 해당 코스의 체크 포인트로 간주해라!</x:t>
   </x:si>
   <x:si>
+    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
     <x:t>후크</x:t>
   </x:si>
   <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
   </x:si>
   <x:si>
     <x:t>id</x:t>
   </x:si>
   <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 에디터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다.</x:t>
   </x:si>
   <x:si>
     <x:t>text</x:t>
   </x:si>
   <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
     <x:t>스테이지 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체화면</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -143,31 +143,55 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>로딩중...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 에디터</x:t>
+    <x:t>전체화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vsync</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esc를 눌러 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 재시작</x:t>
   </x:si>
   <x:si>
     <x:t>슈퍼 솔저 캠프에 온 것을 환영한다!</x:t>
   </x:si>
   <x:si>
-    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 재시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Esc를 눌러 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결에 실패했습니다</x:t>
+    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -306,7 +330,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -334,6 +358,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1120,7 +1150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B43"/>
+  <x:dimension ref="A1:B51"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -1129,10 +1159,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1140,7 +1170,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1148,7 +1178,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1156,7 +1186,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1164,7 +1194,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1172,7 +1202,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1188,7 +1218,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1196,7 +1226,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1204,7 +1234,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1212,7 +1242,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1228,7 +1258,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1236,7 +1266,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1244,7 +1274,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1252,7 +1282,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1268,7 +1298,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1276,7 +1306,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1284,7 +1314,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2" ht="17.149999999999999">
@@ -1300,7 +1330,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1308,7 +1338,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1316,7 +1346,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1324,7 +1354,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1332,7 +1362,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1340,7 +1370,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1348,7 +1378,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1356,7 +1386,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1364,7 +1394,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1372,7 +1402,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1380,7 +1410,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1388,7 +1418,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1396,7 +1426,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1404,7 +1434,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1412,7 +1442,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1420,7 +1450,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1428,7 +1458,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1436,7 +1466,7 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>38</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1444,7 +1474,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1468,11 +1498,75 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:2">
+      <x:c r="A44">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="B44" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:2">
+      <x:c r="A45">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:2">
+      <x:c r="A46">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="B46" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:2">
+      <x:c r="A47">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="B47" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:2">
+      <x:c r="A48">
+        <x:v>70001</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:2">
+      <x:c r="A49">
+        <x:v>70010</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:2">
+      <x:c r="A50">
+        <x:v>70011</x:v>
+      </x:c>
+      <x:c r="B50" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:2">
+      <x:c r="A51">
+        <x:v>70012</x:v>
+      </x:c>
+      <x:c r="B51" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -15,106 +15,106 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋아, 콩알 파이프를 활성화하게 되면, 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
     <x:t>네 멍청한 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
   </x:si>
   <x:si>
-    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋아, 콩알 파이프를 활성화하게 되면, 해당 코스의 체크 포인트로 간주해라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
   </x:si>
   <x:si>
     <x:t>타이틀</x:t>
   </x:si>
   <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
     <x:t>마스터</x:t>
   </x:si>
   <x:si>
     <x:t>id</x:t>
   </x:si>
   <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 에디터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩중...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -149,12 +149,39 @@
     <x:t>Vsync</x:t>
   </x:si>
   <x:si>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 에디터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
     <x:t>Esc를 눌러 종료</x:t>
   </x:si>
   <x:si>
-    <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
     <x:t>인게임에서는 비활성화</x:t>
   </x:si>
   <x:si>
@@ -164,34 +191,7 @@
     <x:t>슈퍼 솔저 캠프에 온 것을 환영한다!</x:t>
   </x:si>
   <x:si>
-    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -376,6 +376,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -420,6 +421,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -496,6 +498,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -534,6 +537,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -556,6 +560,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -588,6 +593,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -635,6 +641,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -690,6 +697,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -724,6 +732,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -756,6 +765,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -778,6 +788,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1159,10 +1170,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1170,7 +1181,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1178,7 +1189,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1186,7 +1197,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1194,7 +1205,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1202,7 +1213,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1210,7 +1221,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1226,7 +1237,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1234,7 +1245,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1242,7 +1253,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1250,7 +1261,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1258,7 +1269,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1274,7 +1285,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1282,7 +1293,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1290,7 +1301,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1298,7 +1309,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1306,7 +1317,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1314,7 +1325,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2" ht="17.149999999999999">
@@ -1330,7 +1341,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1338,7 +1349,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1346,7 +1357,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1354,7 +1365,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1362,7 +1373,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1370,7 +1381,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1378,7 +1389,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1386,7 +1397,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1394,7 +1405,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1402,7 +1413,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1410,7 +1421,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1418,7 +1429,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1426,7 +1437,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1434,7 +1445,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1442,7 +1453,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1450,7 +1461,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>46</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1458,7 +1469,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>47</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1466,7 +1477,7 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1474,7 +1485,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1482,7 +1493,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1490,7 +1501,7 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1498,7 +1509,7 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1506,7 +1517,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1514,7 +1525,7 @@
         <x:v>50001</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:2">
@@ -1522,7 +1533,7 @@
         <x:v>50002</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:2">
@@ -1530,7 +1541,7 @@
         <x:v>50003</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
@@ -1538,7 +1549,7 @@
         <x:v>70001</x:v>
       </x:c>
       <x:c r="B48" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -1546,7 +1557,7 @@
         <x:v>70010</x:v>
       </x:c>
       <x:c r="B49" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
@@ -1554,7 +1565,7 @@
         <x:v>70011</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
@@ -1562,7 +1573,7 @@
         <x:v>70012</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -13,63 +13,195 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+  <x:si>
+    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네 모자란 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크를 걸어둔 채로, 좌우로 흔들어 더 멀리 이동할 수도 있으니 잘 활용해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 잘 활용해서 장애물을 넘어가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>준비중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
+  </x:si>
   <x:si>
     <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
   </x:si>
   <x:si>
-    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋아, 콩알 파이프를 활성화하게 되면, 해당 코스의 체크 포인트로 간주해라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
-  </x:si>
-  <x:si>
     <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
   </x:si>
   <x:si>
     <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
   </x:si>
   <x:si>
-    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오브젝트 재생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 재시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esc를 눌러 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>색상선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커서색상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수직동기화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 에디터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
   </x:si>
   <x:si>
     <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체화면</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -98,118 +230,55 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>로딩중...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 에디터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수직동기화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커서색상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>색상선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건 첫 번째 튜토리얼 코스다. 만약 너희가 다람쥐보단 똑똑하다면, 문제 될 것이 없다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네 멍청한 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오브젝트 재생성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 재시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Esc를 눌러 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈퍼 솔저 캠프에 온 것을 환영한다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>준비중</x:t>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(알 수 없는 환호 소리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 그래플링 후크의 기본을 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머리 쓰려다가 폭발하지나 말았으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(고개를 끄덕임)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한번 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 초간단 퍼즐이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 듣도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -834,7 +903,7 @@
       </x:fill>
     </x:dxf>
   </x:dxfs>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="PivotStyleLight16" pivot="1" table="0" count="11">
       <x:tableStyleElement type="headerRow" size="1" dxfId="0"/>
       <x:tableStyleElement type="totalRow" size="1" dxfId="1"/>
@@ -1173,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B57"/>
+  <x:dimension ref="A1:B81"/>
   <x:sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -1182,10 +1251,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>12</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1193,7 +1262,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>48</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1201,7 +1270,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1209,7 +1278,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1217,7 +1286,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1225,7 +1294,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1233,7 +1302,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1241,7 +1310,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1249,7 +1318,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1257,7 +1326,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1265,7 +1334,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1273,7 +1342,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1281,7 +1350,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1289,7 +1358,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1297,7 +1366,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1305,7 +1374,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1313,7 +1382,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1321,7 +1390,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1329,7 +1398,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1337,7 +1406,7 @@
         <x:v>1018</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1345,7 +1414,7 @@
         <x:v>1019</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1353,7 +1422,7 @@
         <x:v>1020</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1361,7 +1430,7 @@
         <x:v>1021</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1369,7 +1438,7 @@
         <x:v>1022</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1377,7 +1446,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2" ht="17.149999999999999">
@@ -1385,7 +1454,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1393,7 +1462,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1401,7 +1470,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1409,7 +1478,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1417,7 +1486,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1425,7 +1494,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1433,7 +1502,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1441,7 +1510,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1449,7 +1518,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1457,7 +1526,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1465,7 +1534,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1473,7 +1542,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1481,7 +1550,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1489,7 +1558,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1497,7 +1566,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>39</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1505,7 +1574,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>4</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1513,7 +1582,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1521,7 +1590,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1529,7 +1598,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1537,103 +1606,289 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:2">
-      <x:c r="A46">
-        <x:v>10007</x:v>
-      </x:c>
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="2:2">
       <x:c r="B46" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:2">
-      <x:c r="A47">
-        <x:v>10008</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="2:2">
       <x:c r="B47" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
       <x:c r="A48">
-        <x:v>10009</x:v>
+        <x:v>10007</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
       <x:c r="A49">
-        <x:v>10010</x:v>
+        <x:v>10008</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
       <x:c r="A50">
-        <x:v>50000</x:v>
+        <x:v>10009</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
       <x:c r="A51">
-        <x:v>50001</x:v>
+        <x:v>10010</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
       <x:c r="A52">
-        <x:v>50002</x:v>
+        <x:v>10100</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>7</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
       <x:c r="A53">
-        <x:v>50003</x:v>
+        <x:v>10101</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>5</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
       <x:c r="A54">
-        <x:v>70001</x:v>
+        <x:v>10102</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
       <x:c r="A55">
-        <x:v>70010</x:v>
-      </x:c>
-      <x:c r="B55" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>10103</x:v>
+      </x:c>
+      <x:c r="B55" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
       <x:c r="A56">
-        <x:v>70011</x:v>
+        <x:v>10104</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
       <x:c r="A57">
+        <x:v>10105</x:v>
+      </x:c>
+      <x:c r="B57" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:2">
+      <x:c r="A58">
+        <x:v>10106</x:v>
+      </x:c>
+      <x:c r="B58" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:2">
+      <x:c r="A59">
+        <x:v>10107</x:v>
+      </x:c>
+      <x:c r="B59" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:2">
+      <x:c r="A60">
+        <x:v>10108</x:v>
+      </x:c>
+      <x:c r="B60" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:2">
+      <x:c r="A61">
+        <x:v>10109</x:v>
+      </x:c>
+      <x:c r="B61" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:2">
+      <x:c r="A62">
+        <x:v>10110</x:v>
+      </x:c>
+      <x:c r="B62" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:2">
+      <x:c r="A63">
+        <x:v>10111</x:v>
+      </x:c>
+      <x:c r="B63" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:2">
+      <x:c r="A64">
+        <x:v>10112</x:v>
+      </x:c>
+      <x:c r="B64" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:2">
+      <x:c r="A65">
+        <x:v>10113</x:v>
+      </x:c>
+      <x:c r="B65" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:2">
+      <x:c r="A66">
+        <x:v>10114</x:v>
+      </x:c>
+      <x:c r="B66" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:2">
+      <x:c r="A67">
+        <x:v>10115</x:v>
+      </x:c>
+      <x:c r="B67" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:2">
+      <x:c r="A68">
+        <x:v>10116</x:v>
+      </x:c>
+      <x:c r="B68" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:2">
+      <x:c r="A69">
+        <x:v>10117</x:v>
+      </x:c>
+      <x:c r="B69" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:2">
+      <x:c r="A70">
+        <x:v>10118</x:v>
+      </x:c>
+      <x:c r="B70" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:2">
+      <x:c r="A71">
+        <x:v>10119</x:v>
+      </x:c>
+      <x:c r="B71" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:2">
+      <x:c r="A72">
+        <x:v>10120</x:v>
+      </x:c>
+      <x:c r="B72" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:2">
+      <x:c r="A73">
+        <x:v>10121</x:v>
+      </x:c>
+      <x:c r="B73" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:2">
+      <x:c r="A74">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="B74" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:2">
+      <x:c r="A75">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="B75" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:2">
+      <x:c r="A76">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="B76" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:2">
+      <x:c r="A77">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="B77" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:2">
+      <x:c r="A78">
+        <x:v>70001</x:v>
+      </x:c>
+      <x:c r="B78" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:2">
+      <x:c r="A79">
+        <x:v>70010</x:v>
+      </x:c>
+      <x:c r="B79" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:2">
+      <x:c r="A80">
+        <x:v>70011</x:v>
+      </x:c>
+      <x:c r="B80" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:2">
+      <x:c r="A81">
         <x:v>70012</x:v>
       </x:c>
-      <x:c r="B57" t="s">
-        <x:v>8</x:v>
+      <x:c r="B81" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -13,63 +13,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+  <x:si>
+    <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 듣도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
+  </x:si>
   <x:si>
     <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
+  </x:si>
+  <x:si>
     <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
   </x:si>
   <x:si>
+    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
+  </x:si>
+  <x:si>
     <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
   </x:si>
   <x:si>
+    <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
+  <x:si>
     <x:t>네 모자란 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
   </x:si>
   <x:si>
     <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
   </x:si>
   <x:si>
+    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야, 어디로 간 거지? 신호도 안 잡히고 카메라에도 보이질 않...ㅈ...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+  </x:si>
+  <x:si>
     <x:t>후크를 걸어둔 채로, 좌우로 흔들어 더 멀리 이동할 수도 있으니 잘 활용해 보아라.</x:t>
   </x:si>
   <x:si>
-    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
+    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 사회에 쓸모 있는 콩알들이 되고 엄숙한 의무를 다할 수 있도록 돕는 곳이지!</x:t>
   </x:si>
   <x:si>
     <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
   </x:si>
   <x:si>
-    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
-  </x:si>
-  <x:si>
     <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 잘 활용해서 장애물을 넘어가도록.</x:t>
   </x:si>
   <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
     <x:t>id</x:t>
   </x:si>
   <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취소</x:t>
+  </x:si>
+  <x:si>
     <x:t>종료</x:t>
   </x:si>
   <x:si>
-    <x:t>취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
+    <x:t>준비중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
   </x:si>
   <x:si>
     <x:t>해상도</x:t>
@@ -78,130 +135,127 @@
     <x:t>한국어</x:t>
   </x:si>
   <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
     <x:t>언어</x:t>
   </x:si>
   <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>준비중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+    <x:t>(알 수 없는 환호 소리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 초간단 퍼즐이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
   </x:si>
   <x:si>
     <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
   </x:si>
   <x:si>
-    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
+    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 연습 코스를 모두...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠장! 어디 있다가 튀어나온 거야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
   </x:si>
   <x:si>
     <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
   </x:si>
   <x:si>
-    <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
+    <x:t>한참 동안 없어졌길래 실험 실패로 폐기처분할까 했더니 그래도 돌아왔군.</x:t>
   </x:si>
   <x:si>
     <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
   </x:si>
   <x:si>
-    <x:t>너희들이 쓸모 있는 콩알들이 되고 엄숙한 의무를 다하도록 돕는 곳이지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
-  </x:si>
-  <x:si>
     <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
   </x:si>
   <x:si>
+    <x:t>이번에는 좀 더 다양한 물건들에 대해 배워보는 코스다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
   </x:si>
   <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+    <x:t>적당히 뒤에 보이는 텔레포터 너머에 둘 테니 가져가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앞에 보이는 빨간 장벽은 유기물을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(고개를 끄덕임)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esc를 눌러 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 재시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한번 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
   </x:si>
   <x:si>
     <x:t>오브젝트 재생성</x:t>
   </x:si>
   <x:si>
-    <x:t>스테이지 재시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Esc를 눌러 종료</x:t>
+    <x:t>커서색상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 에디터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수직동기화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
   </x:si>
   <x:si>
     <x:t>색상선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커서색상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수직동기화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 에디터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩중...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체화면</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -230,55 +284,40 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(알 수 없는 환호 소리)</x:t>
+    <x:t>아 이런 열쇠를 배치하는 것을 까먹었군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>훈련 코스의 마지막이니 한번 잘 해보도록.</x:t>
   </x:si>
   <x:si>
     <x:t>여기선 그래플링 후크의 기본을 알려주겠다.</x:t>
   </x:si>
   <x:si>
+    <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>머리 쓰려다가 폭발하지나 말았으면 좋겠군.</x:t>
   </x:si>
   <x:si>
-    <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
   </x:si>
   <x:si>
     <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
   </x:si>
   <x:si>
-    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(고개를 끄덕임)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한번 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바로 초간단 퍼즐이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 듣도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
+    <x:t>크게 어렵거나 한 것은 아니지만 좀 더 위험한 것들이 많지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(스피커 잡음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔 일이 있었는지 모르겠지만, 뭐 돌아왔으니 어서 코스나 마무리하도록 하자고, 알겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일전에 보았을 파란 장벽과는 반대되는 기능을 가진 셈이지. 그러니까... 뭐 만지지 말라고.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1242,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B81"/>
+  <x:dimension ref="A1:B94"/>
   <x:sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -1251,10 +1290,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>62</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1262,7 +1301,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1270,7 +1309,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1278,7 +1317,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1286,7 +1325,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1294,7 +1333,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1302,7 +1341,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1310,7 +1349,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1318,7 +1357,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1326,7 +1365,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1334,7 +1373,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1342,7 +1381,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1350,7 +1389,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1358,7 +1397,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1366,7 +1405,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1374,7 +1413,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1382,7 +1421,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1390,7 +1429,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1398,7 +1437,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1406,7 +1445,7 @@
         <x:v>1018</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1414,7 +1453,7 @@
         <x:v>1019</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1422,7 +1461,7 @@
         <x:v>1020</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1430,7 +1469,7 @@
         <x:v>1021</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1438,7 +1477,7 @@
         <x:v>1022</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1446,7 +1485,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2" ht="17.149999999999999">
@@ -1454,7 +1493,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1462,7 +1501,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1470,7 +1509,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1478,7 +1517,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1486,7 +1525,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1494,7 +1533,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1502,7 +1541,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1510,7 +1549,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1518,7 +1557,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1526,7 +1565,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1534,7 +1573,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1542,7 +1581,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1550,7 +1589,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1558,7 +1597,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1566,7 +1605,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1574,7 +1613,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1582,7 +1621,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1590,7 +1629,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1598,7 +1637,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>65</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1606,17 +1645,17 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>71</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="2:2">
       <x:c r="B46" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="2:2">
       <x:c r="B47" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
@@ -1624,7 +1663,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -1632,7 +1671,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
@@ -1640,7 +1679,7 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
@@ -1648,7 +1687,7 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
@@ -1656,7 +1695,7 @@
         <x:v>10100</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>66</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
@@ -1664,7 +1703,7 @@
         <x:v>10101</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>77</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
@@ -1672,7 +1711,7 @@
         <x:v>10102</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>34</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
@@ -1680,7 +1719,7 @@
         <x:v>10103</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
@@ -1688,7 +1727,7 @@
         <x:v>10104</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
@@ -1696,7 +1735,7 @@
         <x:v>10105</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
@@ -1704,7 +1743,7 @@
         <x:v>10106</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
@@ -1712,7 +1751,7 @@
         <x:v>10107</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
@@ -1720,7 +1759,7 @@
         <x:v>10108</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>78</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
@@ -1728,7 +1767,7 @@
         <x:v>10109</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:2">
@@ -1736,7 +1775,7 @@
         <x:v>10110</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>69</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
@@ -1744,7 +1783,7 @@
         <x:v>10111</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:2">
@@ -1752,7 +1791,7 @@
         <x:v>10112</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:2">
@@ -1760,7 +1799,7 @@
         <x:v>10113</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:2">
@@ -1768,7 +1807,7 @@
         <x:v>10114</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:2">
@@ -1776,7 +1815,7 @@
         <x:v>10115</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>76</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:2">
@@ -1784,7 +1823,7 @@
         <x:v>10116</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:2">
@@ -1792,7 +1831,7 @@
         <x:v>10117</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:2">
@@ -1800,7 +1839,7 @@
         <x:v>10118</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:2">
@@ -1808,7 +1847,7 @@
         <x:v>10119</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>67</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:2">
@@ -1816,7 +1855,7 @@
         <x:v>10120</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>80</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:2">
@@ -1824,71 +1863,175 @@
         <x:v>10121</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:2">
       <x:c r="A74">
-        <x:v>50000</x:v>
+        <x:v>10122</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:2">
       <x:c r="A75">
-        <x:v>50001</x:v>
+        <x:v>10123</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>31</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:2">
       <x:c r="A76">
-        <x:v>50002</x:v>
+        <x:v>10124</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>42</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:2">
       <x:c r="A77">
-        <x:v>50003</x:v>
+        <x:v>10125</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:2">
       <x:c r="A78">
-        <x:v>70001</x:v>
+        <x:v>10126</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>6</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:2">
       <x:c r="A79">
-        <x:v>70010</x:v>
-      </x:c>
-      <x:c r="B79" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>10127</x:v>
+      </x:c>
+      <x:c r="B79" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:2">
       <x:c r="A80">
-        <x:v>70011</x:v>
+        <x:v>10128</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:2">
       <x:c r="A81">
+        <x:v>10129</x:v>
+      </x:c>
+      <x:c r="B81" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:2">
+      <x:c r="A82">
+        <x:v>10130</x:v>
+      </x:c>
+      <x:c r="B82" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:2">
+      <x:c r="A83">
+        <x:v>10131</x:v>
+      </x:c>
+      <x:c r="B83" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:2">
+      <x:c r="A84">
+        <x:v>10132</x:v>
+      </x:c>
+      <x:c r="B84" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:2">
+      <x:c r="A85">
+        <x:v>10133</x:v>
+      </x:c>
+      <x:c r="B85" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:2">
+      <x:c r="A86">
+        <x:v>10134</x:v>
+      </x:c>
+      <x:c r="B86" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:2">
+      <x:c r="A87">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="B87" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:2">
+      <x:c r="A88">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="B88" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:2">
+      <x:c r="A89">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="B89" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:2">
+      <x:c r="A90">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="B90" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:2">
+      <x:c r="A91">
+        <x:v>70001</x:v>
+      </x:c>
+      <x:c r="B91" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:2">
+      <x:c r="A92">
+        <x:v>70010</x:v>
+      </x:c>
+      <x:c r="B92" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:2">
+      <x:c r="A93">
+        <x:v>70011</x:v>
+      </x:c>
+      <x:c r="B93" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:2">
+      <x:c r="A94">
         <x:v>70012</x:v>
       </x:c>
-      <x:c r="B81" t="s">
-        <x:v>43</x:v>
+      <x:c r="B94" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -13,7 +13,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+  <x:si>
+    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네 모자란 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상에, 이번 코스도 통과하다니 콩알 놈들 중에선 상위 0.1%는 될 거 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>준비중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옵션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참가</x:t>
+  </x:si>
   <x:si>
     <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 듣도록.</x:t>
   </x:si>
@@ -21,229 +87,196 @@
     <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
   </x:si>
   <x:si>
+    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크게 어렵거나 한 것은 아니지만 좀 더 위험한 것들이 많지.</x:t>
+  </x:si>
+  <x:si>
     <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
   </x:si>
   <x:si>
     <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+    <x:t>뭐야, 어디로 간 거지? 신호도 안 잡히고 카메라에도 보이질 않...ㅈ...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 기본적인 조작을 익혔으니 다른 물건들을 연습할 코스를 준비했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장치에 적힌 순서를 보고 맞는 번호의 구체들을 연결해주면, 끝인 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>솔직히, 첫 번째 코스도 통과 못 하는 놈들이 많아 얼마 만에 쓰는 코스인지 모르겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일전에 보았을 파란 장벽과는 반대되는 기능을 가진 셈이지. 그러니까... 뭐 만지지 말라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔 일이 있었는지 모르겠지만, 뭐 돌아왔으니 어서 코스나 마무리하도록 하자고, 알겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
   </x:si>
   <x:si>
     <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네 모자란 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
   </x:si>
   <x:si>
-    <x:t>뭐야, 어디로 간 거지? 신호도 안 잡히고 카메라에도 보이질 않...ㅈ...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+    <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 앞에 있는 풍선 퍼즐에 대해 설명해 주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래는 여러가지 추리 과정을 거치는 퍼즐이었지만,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 구체들을 담을 장치들이 벽에 붙어있을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠장! 어디 있다가 튀어나온 거야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 연습 코스를 모두...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(알 수 없는 환호 소리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바로 초간단 퍼즐이지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esc를 눌러 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(고개를 끄덕임)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 재시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오브젝트 재생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한번 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(스피커 잡음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 잘 활용해서 장애물을 넘어가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직접 들고 다닐 수 있는 레이저 반사 박스와 각도를 조작할 수 있는 유리들이 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 사회에 쓸모 있는 콩알들이 되고 엄숙한 의무를 다할 수 있도록 돕는 곳이지!</x:t>
   </x:si>
   <x:si>
     <x:t>후크를 걸어둔 채로, 좌우로 흔들어 더 멀리 이동할 수도 있으니 잘 활용해 보아라.</x:t>
   </x:si>
   <x:si>
-    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희들이 사회에 쓸모 있는 콩알들이 되고 엄숙한 의무를 다할 수 있도록 돕는 곳이지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 잘 활용해서 장애물을 넘어가도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>준비중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옵션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(알 수 없는 환호 소리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바로 초간단 퍼즐이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다. 연습 코스를 모두...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠장! 어디 있다가 튀어나온 거야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+    <x:t>풍선 기구가 배치되어있다면 그곳에는 숫자가 적힌 에너지 구체들이 흩뿌려져 있을 것이고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
   </x:si>
   <x:si>
     <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
   </x:si>
   <x:si>
-    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
+    <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
   </x:si>
   <x:si>
     <x:t>한참 동안 없어졌길래 실험 실패로 폐기처분할까 했더니 그래도 돌아왔군.</x:t>
   </x:si>
   <x:si>
-    <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 좀 더 다양한 물건들에 대해 배워보는 코스다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적당히 뒤에 보이는 텔레포터 너머에 둘 테니 가져가도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앞에 보이는 빨간 장벽은 유기물을 제거하는 장치다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(고개를 끄덕임)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Esc를 눌러 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 재시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한번 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오브젝트 재생성</x:t>
+    <x:t>게임 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로딩중...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임 참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 에디터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코드 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
   </x:si>
   <x:si>
     <x:t>커서색상</x:t>
   </x:si>
   <x:si>
-    <x:t>게임 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로딩중...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>접속 코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
-  </x:si>
-  <x:si>
     <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임 참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 에디터</x:t>
   </x:si>
   <x:si>
     <x:t>전체화면</x:t>
@@ -284,40 +317,58 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 좀 더 다양한 물건들에 대해 배워보는 코스다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앞에 보이는 빨간 장벽은 유기물을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적당히 뒤에 보이는 텔레포터 너머에 둘 테니 가져가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 뒤에는 여러 레이저를 조작하는 물건들이 놓여있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주변만 잘 살펴봐도 전혀 어려울 것이 없을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>훈련 코스의 마지막이니 한번 잘 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 그래플링 후크의 기본을 알려주겠다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>아 이런 열쇠를 배치하는 것을 까먹었군.</x:t>
   </x:si>
   <x:si>
-    <x:t>훈련 코스의 마지막이니 한번 잘 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기선 그래플링 후크의 기본을 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
-  </x:si>
-  <x:si>
     <x:t>머리 쓰려다가 폭발하지나 말았으면 좋겠군.</x:t>
   </x:si>
   <x:si>
-    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크게 어렵거나 한 것은 아니지만 좀 더 위험한 것들이 많지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(스피커 잡음)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭔 일이 있었는지 모르겠지만, 뭐 돌아왔으니 어서 코스나 마무리하도록 하자고, 알겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일전에 보았을 파란 장벽과는 반대되는 기능을 가진 셈이지. 그러니까... 뭐 만지지 말라고.</x:t>
+    <x:t>레이저를 위주로 배울 예정이니 쓸데없이 건드리다 타죽지 말도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 코스의 시작은 지금부터다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설마, 벌써 오는 길에 죽지는 않았겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그걸 해내는 콩알들이 아무도 없었어서 훨씬 간소화 되었지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것들을 잘 활용해 타버리지말고, 이번 코스도 성공해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 후에는 공기총으로 풍선에 공기를 불어넣어주면, 짜잔! 답을 맞출 수 있다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -496,7 +547,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -541,7 +591,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -618,7 +667,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -657,7 +705,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -680,7 +727,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -713,7 +759,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -761,7 +806,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -817,7 +861,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -852,7 +895,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -885,7 +927,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -908,7 +949,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1281,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B94"/>
+  <x:dimension ref="A1:B111"/>
   <x:sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -1290,10 +1330,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>74</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1301,7 +1341,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1309,7 +1349,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1317,7 +1357,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1325,7 +1365,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1333,7 +1373,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1341,7 +1381,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1349,7 +1389,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1357,7 +1397,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1365,7 +1405,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1373,7 +1413,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1381,7 +1421,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1389,7 +1429,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1397,7 +1437,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1405,7 +1445,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1413,7 +1453,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1421,7 +1461,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1429,7 +1469,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1437,7 +1477,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1445,7 +1485,7 @@
         <x:v>1018</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1453,7 +1493,7 @@
         <x:v>1019</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1461,7 +1501,7 @@
         <x:v>1020</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1469,7 +1509,7 @@
         <x:v>1021</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1477,7 +1517,7 @@
         <x:v>1022</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1485,7 +1525,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2" ht="17.149999999999999">
@@ -1493,7 +1533,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1501,7 +1541,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1509,7 +1549,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1517,7 +1557,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1525,7 +1565,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1533,7 +1573,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1541,7 +1581,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1549,7 +1589,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1557,7 +1597,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1565,7 +1605,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1573,7 +1613,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1581,7 +1621,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1589,7 +1629,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1597,7 +1637,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1605,7 +1645,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>85</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1613,7 +1653,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1621,7 +1661,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>6</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1629,7 +1669,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>21</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1637,7 +1677,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1645,17 +1685,17 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="2:2">
       <x:c r="B46" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="2:2">
       <x:c r="B47" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
@@ -1663,7 +1703,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -1671,7 +1711,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
@@ -1679,7 +1719,7 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
@@ -1687,7 +1727,7 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
@@ -1695,7 +1735,7 @@
         <x:v>10100</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
@@ -1703,7 +1743,7 @@
         <x:v>10101</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
@@ -1711,7 +1751,7 @@
         <x:v>10102</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
@@ -1719,7 +1759,7 @@
         <x:v>10103</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>18</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
@@ -1727,7 +1767,7 @@
         <x:v>10104</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
@@ -1735,7 +1775,7 @@
         <x:v>10105</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
@@ -1743,7 +1783,7 @@
         <x:v>10106</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
@@ -1751,7 +1791,7 @@
         <x:v>10107</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
@@ -1759,7 +1799,7 @@
         <x:v>10108</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
@@ -1767,7 +1807,7 @@
         <x:v>10109</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:2">
@@ -1775,7 +1815,7 @@
         <x:v>10110</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>9</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
@@ -1783,7 +1823,7 @@
         <x:v>10111</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>22</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:2">
@@ -1791,7 +1831,7 @@
         <x:v>10112</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>89</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:2">
@@ -1799,7 +1839,7 @@
         <x:v>10113</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>51</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:2">
@@ -1807,7 +1847,7 @@
         <x:v>10114</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:2">
@@ -1815,7 +1855,7 @@
         <x:v>10115</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:2">
@@ -1823,7 +1863,7 @@
         <x:v>10116</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:2">
@@ -1831,7 +1871,7 @@
         <x:v>10117</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>3</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:2">
@@ -1839,7 +1879,7 @@
         <x:v>10118</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:2">
@@ -1847,7 +1887,7 @@
         <x:v>10119</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:2">
@@ -1855,7 +1895,7 @@
         <x:v>10120</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:2">
@@ -1863,7 +1903,7 @@
         <x:v>10121</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:2">
@@ -1871,7 +1911,7 @@
         <x:v>10122</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>57</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:2">
@@ -1879,7 +1919,7 @@
         <x:v>10123</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:2">
@@ -1887,7 +1927,7 @@
         <x:v>10124</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>83</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:2">
@@ -1895,7 +1935,7 @@
         <x:v>10125</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>60</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:2">
@@ -1903,7 +1943,7 @@
         <x:v>10126</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:2">
@@ -1911,7 +1951,7 @@
         <x:v>10127</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:2">
@@ -1919,7 +1959,7 @@
         <x:v>10128</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>91</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:2">
@@ -1927,7 +1967,7 @@
         <x:v>10129</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:2">
@@ -1935,7 +1975,7 @@
         <x:v>10130</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>54</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:2">
@@ -1943,7 +1983,7 @@
         <x:v>10131</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:2">
@@ -1951,7 +1991,7 @@
         <x:v>10132</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:2">
@@ -1959,7 +1999,7 @@
         <x:v>10133</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>82</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:2">
@@ -1967,71 +2007,207 @@
         <x:v>10134</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>59</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:2">
       <x:c r="A87">
-        <x:v>50000</x:v>
+        <x:v>10135</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:2">
       <x:c r="A88">
-        <x:v>50001</x:v>
+        <x:v>10136</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:2">
       <x:c r="A89">
-        <x:v>50002</x:v>
+        <x:v>10137</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:2">
       <x:c r="A90">
-        <x:v>50003</x:v>
+        <x:v>10138</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>43</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:2">
       <x:c r="A91">
-        <x:v>70001</x:v>
+        <x:v>10139</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>13</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:2">
       <x:c r="A92">
-        <x:v>70010</x:v>
-      </x:c>
-      <x:c r="B92" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>10140</x:v>
+      </x:c>
+      <x:c r="B92" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:2">
       <x:c r="A93">
-        <x:v>70011</x:v>
+        <x:v>10141</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:2">
       <x:c r="A94">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="B94" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:2">
+      <x:c r="A95">
+        <x:v>10143</x:v>
+      </x:c>
+      <x:c r="B95" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:2">
+      <x:c r="A96">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="B96" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:2">
+      <x:c r="A97">
+        <x:v>10145</x:v>
+      </x:c>
+      <x:c r="B97" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:2">
+      <x:c r="A98">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="B98" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:2">
+      <x:c r="A99">
+        <x:v>10147</x:v>
+      </x:c>
+      <x:c r="B99" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:2">
+      <x:c r="A100">
+        <x:v>10148</x:v>
+      </x:c>
+      <x:c r="B100" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:2">
+      <x:c r="A101">
+        <x:v>10149</x:v>
+      </x:c>
+      <x:c r="B101" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:2">
+      <x:c r="A102">
+        <x:v>10150</x:v>
+      </x:c>
+      <x:c r="B102" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:2">
+      <x:c r="A103">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="B103" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:2">
+      <x:c r="A104">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="B104" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:2">
+      <x:c r="A105">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="B105" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:2">
+      <x:c r="A106">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="B106" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:2">
+      <x:c r="A107">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="B107" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:2">
+      <x:c r="A108">
+        <x:v>70001</x:v>
+      </x:c>
+      <x:c r="B108" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:2">
+      <x:c r="A109">
+        <x:v>70010</x:v>
+      </x:c>
+      <x:c r="B109" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:2">
+      <x:c r="A110">
+        <x:v>70011</x:v>
+      </x:c>
+      <x:c r="B110" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:2">
+      <x:c r="A111">
         <x:v>70012</x:v>
       </x:c>
-      <x:c r="B94" t="s">
-        <x:v>58</x:v>
+      <x:c r="B111" t="s">
+        <x:v>96</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/StreamingAssets/Localization/Korean.xlsx
+++ b/Assets/StreamingAssets/Localization/Korean.xlsx
@@ -15,34 +15,139 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <x:si>
+    <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저를 위주로 배울 예정이니 쓸데없이 건드리다 타죽지 말도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것들을 잘 활용해 타버리지말고, 이번 코스도 성공해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그걸 해내는 콩알들이 아무도 없었어서 훨씬 간소화 되었지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크게 어렵거나 한 것은 아니지만 좀 더 위험한 것들이 많지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풍선 기구가 배치되어있다면 그곳에는 숫자가 적힌 에너지 구체들이 흩뿌려져 있을 것이고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세상에, 이번 코스도 통과하다니 콩알 놈들 중에선 상위 0.1%는 될 거 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 기본적인 조작을 익혔으니 다른 물건들을 연습할 코스를 준비했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 한 번 이것저것 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 후에는 공기총으로 풍선에 공기를 불어넣어주면, 짜잔! 답을 맞출 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭐야, 어디로 간 거지? 신호도 안 잡히고 카메라에도 보이질 않...ㅈ...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장치에 적힌 순서를 보고 맞는 번호의 구체들을 연결해주면, 끝인 것이다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>이제, 이게 너희 인생의 첫 번째 '진짜' 장애물이다. 그 바보 같은 사춘기 같은 게 아니라!</x:t>
   </x:si>
   <x:si>
     <x:t>네 모자란 파트너가 죽었어도 걱정하지 말라, 콩알 파이프를 통해 똑같은 클론을 바로 내려 보내주마!</x:t>
   </x:si>
   <x:si>
-    <x:t>세상에, 이번 코스도 통과하다니 콩알 놈들 중에선 상위 0.1%는 될 거 같군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아 참고로 너희가 지나갔을 파란 장벽은 너희와 네 녀석들의 도구를 제외한 물건들을 제거하는 장치다.</x:t>
+    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너희들이 사회에 쓸모 있는 콩알들이 되고 엄숙한 의무를 다할 수 있도록 돕는 곳이지!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직접 들고 다닐 수 있는 레이저 반사 박스와 각도를 조작할 수 있는 유리들이 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>후크를 걸어둔 채로, 좌우로 흔들어 더 멀리 이동할 수도 있으니 잘 활용해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>준비중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스터</x:t>
   </x:si>
   <x:si>
     <x:t>id</x:t>
   </x:si>
   <x:si>
+    <x:t>재시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용</x:t>
+  </x:si>
+  <x:si>
     <x:t>에어</x:t>
   </x:si>
   <x:si>
+    <x:t>효과음</x:t>
+  </x:si>
+  <x:si>
     <x:t>취소</x:t>
   </x:si>
   <x:si>
-    <x:t>준비중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과음</x:t>
+    <x:t>참가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이틀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해상도</x:t>
   </x:si>
   <x:si>
     <x:t>옵션</x:t>
@@ -51,139 +156,94 @@
     <x:t>후크</x:t>
   </x:si>
   <x:si>
-    <x:t>배경음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이틀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료</x:t>
-  </x:si>
-  <x:si>
     <x:t>언어</x:t>
   </x:si>
   <x:si>
-    <x:t>한국어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해상도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 듣도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기적이군. 뇌가 작동하는 실험체들이라니. 도대체 얼마 만인지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희 둘의 콩알 대학 평가 점수에 따르면 이 정도는 손쉽겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그냥 내 말대로 따라서, 준비해 둔 속성 코스를 따라와라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사실 오는 길에 이미 한 번쯤 써봤겠지만, 그래도 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 너희 둘의 도구를 활용해서 간단한 장애물을 통과해 보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈의 갈고리를 이용해 스윙해서 다음 플랫폼으로 이동하라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크게 어렵거나 한 것은 아니지만 좀 더 위험한 것들이 많지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 많이도 죽는군! 그 친구는 현재 [/1번]째 재생성이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장애물을 통과했으니 이제 대부분의 실험체가 떨어지는 구간이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭐야, 어디로 간 거지? 신호도 안 잡히고 카메라에도 보이질 않...ㅈ...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그래, 이제 기본적인 것은 전부 배운 것 같으니 종합 테스트 코스를 시작하지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>죄송합니다! 현재 테스트 빌드에서는 사운드가 포함되어 있지 않습니다! ㅠㅠ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 기본적인 조작을 익혔으니 다른 물건들을 연습할 코스를 준비했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭐야 또 죽었나? 많이 죽을 거라고 생각은 했지만 벌써 [/1번]째로군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장치에 적힌 순서를 보고 맞는 번호의 구체들을 연결해주면, 끝인 것이다.</x:t>
+    <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 구체들을 담을 장치들이 벽에 붙어있을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원래는 여러가지 추리 과정을 거치는 퍼즐이었지만,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 앞에 있는 방에는 단순한 풍선 장치가 있지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자 코스의 시작은 지금부터다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠장! 어디 있다가 튀어나온 거야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수고했다. 연습 코스를 모두...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한참 동안 없어졌길래 실험 실패로 폐기처분할까 했더니 그래도 돌아왔군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일전에 보았을 파란 장벽과는 반대되는 기능을 가진 셈이지. 그러니까... 뭐 만지지 말라고.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔 일이 있었는지 모르겠지만, 뭐 돌아왔으니 어서 코스나 마무리하도록 하자고, 알겠지?</x:t>
   </x:si>
   <x:si>
     <x:t>솔직히, 첫 번째 코스도 통과 못 하는 놈들이 많아 얼마 만에 쓰는 코스인지 모르겠군.</x:t>
   </x:si>
   <x:si>
-    <x:t>일전에 보았을 파란 장벽과는 반대되는 기능을 가진 셈이지. 그러니까... 뭐 만지지 말라고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭔 일이 있었는지 모르겠지만, 뭐 돌아왔으니 어서 코스나 마무리하도록 하자고, 알겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 잊지 마라. 너희 둘 다 건너야 해. 네놈의 공기총을 창의적으로 사용해 보아라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것이 두 번째 튜토리얼 코스다. 너희 둘은 평균적인 콩알들보다는 더 똑똑한 것 같군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[끔찍하군!] 하지만, 걱정 말라! 우리 슈퍼 연구소의 기술력으로 얼마든지 재생성할 수 있으니!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위에 다용도 드론이 날아다니는 게 보이는가?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에휴... 이전 녀석들보다는 유능했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 이전 놈들과 다르게 성공했으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 앞에 있는 풍선 퍼즐에 대해 설명해 주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>원래는 여러가지 추리 과정을 거치는 퍼즐이었지만,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 구체들을 담을 장치들이 벽에 붙어있을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다. 열쇠는 챙겨왔겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 옵션은 현재 사용할 수 없습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기선 공기총의 기본을 알려주겠다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠장! 어디 있다가 튀어나온 거야!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어서 열쇠나 챙겨서 나오도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수고했다. 연습 코스를 모두...</x:t>
+    <x:t>적당히 뒤에 보이는 텔레포터 너머에 둘 테니 가져가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앞에 보이는 빨간 장벽은 유기물을 제거하는 장치다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이 뒤에는 여러 레이저를 조작하는 물건들이 놓여있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주변만 잘 살펴봐도 전혀 어려울 것이 없을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번에는 좀 더 다양한 물건들에 대해 배워보는 코스다.</x:t>
   </x:si>
   <x:si>
     <x:t>(알 수 없는 환호 소리)</x:t>
@@ -192,64 +252,13 @@
     <x:t>바로 초간단 퍼즐이지.</x:t>
   </x:si>
   <x:si>
-    <x:t>Esc를 눌러 종료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(고개를 끄덕임)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 재시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오브젝트 재생성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연결에 실패했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인게임에서는 비활성화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한번 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(스피커 잡음)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 잘 활용해서 장애물을 넘어가도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋아, 콩알 파이프문을 활성화했군. 파이프를 해당 코스의 체크 포인트로 간주해라!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이건 첫 번째 연습 코스다. 만약 너희가 쥐새끼보단 똑똑하다면, 문제 될 것이 없다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직접 들고 다닐 수 있는 레이저 반사 박스와 각도를 조작할 수 있는 유리들이 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너희들이 사회에 쓸모 있는 콩알들이 되고 엄숙한 의무를 다할 수 있도록 돕는 곳이지!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>후크를 걸어둔 채로, 좌우로 흔들어 더 멀리 이동할 수도 있으니 잘 활용해 보아라.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풍선 기구가 배치되어있다면 그곳에는 숫자가 적힌 에너지 구체들이 흩뿌려져 있을 것이고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽면에 보이는 대로 조작하여 벽에 후크를 걸고 길이를 조절해 보아라.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 물건이나 여기서 들고 나가게 해서는 안 되니까 말이야. 그렇지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>녀석이 들고 다니는 물건은 공기총으로 물건을 쏴 맞추면 떨어진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽면에 보이는 조작법대로 공기총을 흡입하고 발사하는 행동을 해보도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한참 동안 없어졌길래 실험 실패로 폐기처분할까 했더니 그래도 돌아왔군.</x:t>
+    <x:t>수직동기화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>색상선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>접속 코드</x:t>
   </x:si>
   <x:si>
     <x:t>게임 종료</x:t>
@@ -258,7 +267,19 @@
     <x:t>로딩중...</x:t>
   </x:si>
   <x:si>
-    <x:t>접속 코드</x:t>
+    <x:t>커서색상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체화면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스테이지 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방 코드 입력</x:t>
   </x:si>
   <x:si>
     <x:t>게임 참가</x:t>
@@ -268,27 +289,6 @@
   </x:si>
   <x:si>
     <x:t>코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스테이지 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커서색상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체화면</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수직동기화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방 코드 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>색상선택</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -317,58 +317,58 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>오래도 걸렸군. 그렇지만 코스는 완주했으니 만족해야겠지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이번에는 좀 더 다양한 물건들에 대해 배워보는 코스다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앞에 보이는 빨간 장벽은 유기물을 제거하는 장치다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 죽었군. 몇 번째더라… 아 그래, [/1번]째군!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적당히 뒤에 보이는 텔레포터 너머에 둘 테니 가져가도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이 뒤에는 여러 레이저를 조작하는 물건들이 놓여있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주변만 잘 살펴봐도 전혀 어려울 것이 없을 것이다.</x:t>
+    <x:t>스테이지 재시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한번 해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오브젝트 재생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연결에 실패했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(고개를 끄덕임)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(스피커 잡음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인게임에서는 비활성화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esc를 눌러 종료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아 이런 열쇠를 배치하는 것을 까먹었군.</x:t>
   </x:si>
   <x:si>
     <x:t>훈련 코스의 마지막이니 한번 잘 해보도록.</x:t>
   </x:si>
   <x:si>
-    <x:t>여기선 그래플링 후크의 기본을 알려주겠다.</x:t>
+    <x:t>머리 쓰려다가 폭발하지나 말았으면 좋겠군.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설마, 벌써 오는 길에 죽지는 않았겠지?</x:t>
   </x:si>
   <x:si>
     <x:t>슈퍼 솔저 연구실에 온 것을 환영한다!</x:t>
   </x:si>
   <x:si>
-    <x:t>아 이런 열쇠를 배치하는 것을 까먹었군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머리 쓰려다가 폭발하지나 말았으면 좋겠군.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저를 위주로 배울 예정이니 쓸데없이 건드리다 타죽지 말도록.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자 코스의 시작은 지금부터다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설마, 벌써 오는 길에 죽지는 않았겠지?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그걸 해내는 콩알들이 아무도 없었어서 훨씬 간소화 되었지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이것들을 잘 활용해 타버리지말고, 이번 코스도 성공해 보아라.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 후에는 공기총으로 풍선에 공기를 불어넣어주면, 짜잔! 답을 맞출 수 있다.</x:t>
+    <x:t>네놈 친구도 빨아들여서 발사할 수 있고 녀석이 후크를 걸고 있다면 네놈이 녀석에게 날아갈 수도 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 상태로 공기총을 발사하면 튕겨 나갈 수 있으니 여러모로 잘 활용해서 장애물을 넘어가도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 공기총의 기본을 연습해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기선 그래플링 후크의 기본을 연습해보도록.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>움직임도 굼뜬 네놈은 공기총에 더 의존해야 할 테니 잘 써보도록</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1330,10 +1330,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>4</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1341,7 +1341,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1349,7 +1349,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1357,7 +1357,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1365,7 +1365,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1373,7 +1373,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1381,7 +1381,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1389,7 +1389,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="17.149999999999999">
@@ -1397,7 +1397,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1405,7 +1405,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1413,7 +1413,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1421,7 +1421,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1429,7 +1429,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1437,7 +1437,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1445,7 +1445,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1453,7 +1453,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1461,7 +1461,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1469,7 +1469,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1485,7 +1485,7 @@
         <x:v>1018</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1493,7 +1493,7 @@
         <x:v>1019</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1501,7 +1501,7 @@
         <x:v>1020</x:v>
       </x:c>
       <x:c r="B22" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
@@ -1509,7 +1509,7 @@
         <x:v>1021</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
@@ -1517,7 +1517,7 @@
         <x:v>1022</x:v>
       </x:c>
       <x:c r="B24" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
@@ -1525,7 +1525,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2" ht="17.149999999999999">
@@ -1541,7 +1541,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1549,7 +1549,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1557,7 +1557,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B29" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1565,7 +1565,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B30" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1573,7 +1573,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1581,7 +1581,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1589,7 +1589,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1597,7 +1597,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B34" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1605,7 +1605,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B35" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1613,7 +1613,7 @@
         <x:v>2012</x:v>
       </x:c>
       <x:c r="B36" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1621,7 +1621,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B37" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1629,7 +1629,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1637,7 +1637,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1645,7 +1645,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1653,7 +1653,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1661,7 +1661,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1669,7 +1669,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1677,7 +1677,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>57</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1685,17 +1685,17 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="2:2">
       <x:c r="B46" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="2:2">
       <x:c r="B47" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
@@ -1703,7 +1703,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>41</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -1711,7 +1711,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
@@ -1719,7 +1719,7 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
@@ -1727,7 +1727,7 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>42</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
@@ -1735,7 +1735,7 @@
         <x:v>10100</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>101</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
@@ -1743,7 +1743,7 @@
         <x:v>10101</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
@@ -1751,7 +1751,7 @@
         <x:v>10102</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
@@ -1759,7 +1759,7 @@
         <x:v>10103</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
@@ -1767,7 +1767,7 @@
         <x:v>10104</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
@@ -1775,7 +1775,7 @@
         <x:v>10105</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
@@ -1783,7 +1783,7 @@
         <x:v>10106</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>60</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
@@ -1791,7 +1791,7 @@
         <x:v>10107</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>53</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
@@ -1799,7 +1799,7 @@
         <x:v>10108</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>22</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
@@ -1807,7 +1807,7 @@
         <x:v>10109</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:2">
@@ -1815,7 +1815,7 @@
         <x:v>10110</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>43</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
@@ -1823,7 +1823,7 @@
         <x:v>10111</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>67</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:2">
@@ -1831,7 +1831,7 @@
         <x:v>10112</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:2">
@@ -1839,7 +1839,7 @@
         <x:v>10113</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>76</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:2">
@@ -1847,7 +1847,7 @@
         <x:v>10114</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>65</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:2">
@@ -1855,7 +1855,7 @@
         <x:v>10115</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>27</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:2">
@@ -1863,7 +1863,7 @@
         <x:v>10116</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:2">
@@ -1871,7 +1871,7 @@
         <x:v>10117</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:2">
@@ -1879,7 +1879,7 @@
         <x:v>10118</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>58</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:2">
@@ -1887,7 +1887,7 @@
         <x:v>10119</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:2">
@@ -1895,7 +1895,7 @@
         <x:v>10120</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:2">
@@ -1903,7 +1903,7 @@
         <x:v>10121</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:2">
@@ -1911,7 +1911,7 @@
         <x:v>10122</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>94</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:2">
@@ -1919,7 +1919,7 @@
         <x:v>10123</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:2">
@@ -1927,7 +1927,7 @@
         <x:v>10124</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:2">
@@ -1935,7 +1935,7 @@
         <x:v>10125</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>95</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:2">
@@ -1943,7 +1943,7 @@
         <x:v>10126</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>39</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:2">
@@ -1951,7 +1951,7 @@
         <x:v>10127</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:2">
@@ -1959,7 +1959,7 @@
         <x:v>10128</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>66</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:2">
@@ -1967,7 +1967,7 @@
         <x:v>10129</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:2">
@@ -1975,7 +1975,7 @@
         <x:v>10130</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:2">
@@ -1983,7 +1983,7 @@
         <x:v>10131</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:2">
@@ -1991,7 +1991,7 @@
         <x:v>10132</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:2">
@@ -1999,7 +1999,7 @@
         <x:v>10133</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:2">
@@ -2007,7 +2007,7 @@
         <x:v>10134</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:2">
@@ -2015,7 +2015,7 @@
         <x:v>10135</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:2">
@@ -2023,7 +2023,7 @@
         <x:v>10136</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>105</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:2">
@@ -2031,7 +2031,7 @@
         <x:v>10137</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>38</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:2">
@@ -2039,7 +2039,7 @@
         <x:v>10138</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>106</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:2">
@@ -2047,7 +2047,7 @@
         <x:v>10139</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:2">
@@ -2055,7 +2055,7 @@
         <x:v>10140</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>98</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:2">
@@ -2063,7 +2063,7 @@
         <x:v>10141</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>70</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:2">
@@ -2071,7 +2071,7 @@
         <x:v>10142</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>109</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:2">
@@ -2079,7 +2079,7 @@
         <x:v>10143</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:2">
@@ -2087,7 +2087,7 @@
         <x:v>10144</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>73</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:2">
@@ -2103,7 +2103,7 @@
         <x:v>10146</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:2">
@@ -2111,7 +2111,7 @@
         <x:v>10147</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>110</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:2">
@@ -2119,7 +2119,7 @@
         <x:v>10148</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:2">
@@ -2127,7 +2127,7 @@
         <x:v>10149</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>108</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:2">
@@ -2135,7 +2135,7 @@
         <x:v>10150</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>99</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:2">
@@ -2143,7 +2143,7 @@
         <x:v>10151</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:2">
@@ -2151,7 +2151,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:2">
@@ -2159,7 +2159,7 @@
         <x:v>50001</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:2">
@@ -2167,7 +2167,7 @@
         <x:v>50002</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>93</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:2">
@@ -2175,7 +2175,7 @@
         <x:v>50003</x:v>
       </x:c>
       <x:c r="B107" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:2">
@@ -2183,7 +2183,7 @@
         <x:v>70001</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:2">
@@ -2191,7 +2191,7 @@
         <x:v>70010</x:v>
       </x:c>
       <x:c r="B109" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:2">
@@ -2199,7 +2199,7 @@
         <x:v>70011</x:v>
       </x:c>
       <x:c r="B110" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:2">
@@ -2207,7 +2207,7 @@
         <x:v>70012</x:v>
       </x:c>
       <x:c r="B111" t="s">
-        <x:v>96</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
